--- a/research/traditional_assets/database/data/oman/oman_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_beverage_soft.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0039</v>
+        <v>0.00105</v>
       </c>
       <c r="G2">
-        <v>0.03173553719008265</v>
+        <v>0.002203389830508475</v>
       </c>
       <c r="H2">
-        <v>0.03173553719008265</v>
+        <v>0.002203389830508475</v>
       </c>
       <c r="I2">
-        <v>-0.03603305785123967</v>
+        <v>-0.0235593220338983</v>
       </c>
       <c r="J2">
-        <v>-0.03603305785123967</v>
+        <v>-0.0235593220338983</v>
       </c>
       <c r="K2">
-        <v>-0.67</v>
+        <v>-0.216</v>
       </c>
       <c r="L2">
-        <v>-0.05537190082644629</v>
+        <v>-0.01830508474576271</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.135</v>
+        <v>0.151</v>
       </c>
       <c r="V2">
-        <v>0.0108</v>
+        <v>0.01348214285714286</v>
       </c>
       <c r="W2">
-        <v>-0.07827102803738317</v>
+        <v>-0.02830930537352556</v>
       </c>
       <c r="X2">
-        <v>0.1487085341695845</v>
+        <v>0.1023548038110225</v>
       </c>
       <c r="Y2">
-        <v>-0.2269795622069676</v>
+        <v>-0.130664109184548</v>
       </c>
       <c r="Z2">
-        <v>1.146702047005307</v>
+        <v>1.237545883586786</v>
       </c>
       <c r="AA2">
-        <v>-0.04131918119787718</v>
+        <v>-0.0291557420031463</v>
       </c>
       <c r="AB2">
-        <v>0.140104582301313</v>
+        <v>0.09667948096480963</v>
       </c>
       <c r="AC2">
-        <v>-0.1814237634991901</v>
+        <v>-0.1258352229679559</v>
       </c>
       <c r="AD2">
-        <v>2.04</v>
+        <v>2.27</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2.04</v>
+        <v>2.27</v>
       </c>
       <c r="AG2">
-        <v>1.905</v>
+        <v>2.119</v>
       </c>
       <c r="AH2">
-        <v>0.140302613480055</v>
+        <v>0.1685226429101708</v>
       </c>
       <c r="AI2">
-        <v>0.2109617373319545</v>
+        <v>0.2394514767932489</v>
       </c>
       <c r="AJ2">
-        <v>0.1322457480041652</v>
+        <v>0.1590960282303477</v>
       </c>
       <c r="AK2">
-        <v>0.199790246460409</v>
+        <v>0.2271411726873191</v>
       </c>
       <c r="AL2">
-        <v>0.132</v>
+        <v>0.177</v>
       </c>
       <c r="AM2">
-        <v>0.132</v>
+        <v>0.107</v>
       </c>
       <c r="AN2">
-        <v>7.010309278350516</v>
+        <v>12.82485875706215</v>
       </c>
       <c r="AO2">
-        <v>-3.303030303030303</v>
+        <v>-1.570621468926554</v>
       </c>
       <c r="AP2">
-        <v>6.54639175257732</v>
+        <v>11.97175141242938</v>
       </c>
       <c r="AQ2">
-        <v>-3.303030303030303</v>
+        <v>-2.598130841121496</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0039</v>
+        <v>0.00105</v>
       </c>
       <c r="G3">
-        <v>0.03173553719008265</v>
+        <v>0.002203389830508475</v>
       </c>
       <c r="H3">
-        <v>0.03173553719008265</v>
+        <v>0.002203389830508475</v>
       </c>
       <c r="I3">
-        <v>-0.03603305785123967</v>
+        <v>-0.0235593220338983</v>
       </c>
       <c r="J3">
-        <v>-0.03603305785123967</v>
+        <v>-0.0235593220338983</v>
       </c>
       <c r="K3">
-        <v>-0.67</v>
+        <v>-0.216</v>
       </c>
       <c r="L3">
-        <v>-0.05537190082644629</v>
+        <v>-0.01830508474576271</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.135</v>
+        <v>0.151</v>
       </c>
       <c r="V3">
-        <v>0.0108</v>
+        <v>0.01348214285714286</v>
       </c>
       <c r="W3">
-        <v>-0.07827102803738317</v>
+        <v>-0.02830930537352556</v>
       </c>
       <c r="X3">
-        <v>0.1487085341695845</v>
+        <v>0.1023548038110225</v>
       </c>
       <c r="Y3">
-        <v>-0.2269795622069676</v>
+        <v>-0.130664109184548</v>
       </c>
       <c r="Z3">
-        <v>1.146702047005307</v>
+        <v>1.237545883586786</v>
       </c>
       <c r="AA3">
-        <v>-0.04131918119787718</v>
+        <v>-0.0291557420031463</v>
       </c>
       <c r="AB3">
-        <v>0.140104582301313</v>
+        <v>0.09667948096480963</v>
       </c>
       <c r="AC3">
-        <v>-0.1814237634991901</v>
+        <v>-0.1258352229679559</v>
       </c>
       <c r="AD3">
-        <v>2.04</v>
+        <v>2.27</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.04</v>
+        <v>2.27</v>
       </c>
       <c r="AG3">
-        <v>1.905</v>
+        <v>2.119</v>
       </c>
       <c r="AH3">
-        <v>0.140302613480055</v>
+        <v>0.1685226429101708</v>
       </c>
       <c r="AI3">
-        <v>0.2109617373319545</v>
+        <v>0.2394514767932489</v>
       </c>
       <c r="AJ3">
-        <v>0.1322457480041652</v>
+        <v>0.1590960282303477</v>
       </c>
       <c r="AK3">
-        <v>0.199790246460409</v>
+        <v>0.2271411726873191</v>
       </c>
       <c r="AL3">
-        <v>0.132</v>
+        <v>0.177</v>
       </c>
       <c r="AM3">
-        <v>0.132</v>
+        <v>0.107</v>
       </c>
       <c r="AN3">
-        <v>7.010309278350516</v>
+        <v>12.82485875706215</v>
       </c>
       <c r="AO3">
-        <v>-3.303030303030303</v>
+        <v>-1.570621468926554</v>
       </c>
       <c r="AP3">
-        <v>6.54639175257732</v>
+        <v>11.97175141242938</v>
       </c>
       <c r="AQ3">
-        <v>-3.303030303030303</v>
+        <v>-2.598130841121496</v>
       </c>
     </row>
   </sheetData>
